--- a/outputs/Intermittent/Intermittent - Low N_d_report.xlsx
+++ b/outputs/Intermittent/Intermittent - Low N_d_report.xlsx
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.00368635332921</v>
+        <v>5.886198721913009</v>
       </c>
       <c r="E4" t="n">
-        <v>2.087200429997384</v>
+        <v>2.141235445745966</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1999999999999997</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="5">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5137779831968469</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.606411657411131</v>
+        <v>5.839600082457226</v>
       </c>
       <c r="E5" t="n">
-        <v>2.271078602095603</v>
+        <v>2.014573175404234</v>
       </c>
       <c r="F5" t="n">
-        <v>3.703975591392316</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="6">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7779825632353431</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>6.106676178989058</v>
+        <v>6.482457225314368</v>
       </c>
       <c r="E6" t="n">
-        <v>2.386271648451644</v>
+        <v>2.380262157032531</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7743338660130564</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2046583319061483</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.598815030903372</v>
+        <v>5.196742939600083</v>
       </c>
       <c r="E7" t="n">
-        <v>1.974093689979873</v>
+        <v>1.759039330081219</v>
       </c>
       <c r="F7" t="n">
-        <v>11.26984933589712</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="8">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1841924987155334</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.5740128928924</v>
+        <v>5.196742939600083</v>
       </c>
       <c r="E8" t="n">
-        <v>1.980372691518832</v>
+        <v>1.759039330081219</v>
       </c>
       <c r="F8" t="n">
-        <v>11.54286440230741</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="9">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6511442801362479</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>5.229804035149907</v>
+        <v>5.55388579674294</v>
       </c>
       <c r="E9" t="n">
-        <v>2.035752525482658</v>
+        <v>2.061305719570605</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.807599593160454</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="10">
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2.57561761546724</v>
+        <v>2.238843862904013</v>
       </c>
       <c r="E12" t="n">
-        <v>1.373950974708561</v>
+        <v>1.187682203324712</v>
       </c>
       <c r="F12" t="n">
-        <v>1.800000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.642142960886034</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>2.834681052478321</v>
+        <v>2.738843862904013</v>
       </c>
       <c r="E13" t="n">
-        <v>1.581038238166682</v>
+        <v>1.503293767692378</v>
       </c>
       <c r="F13" t="n">
-        <v>4.337639380703639</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.474996404484013</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>2.078029511977796</v>
+        <v>2.256029684601113</v>
       </c>
       <c r="E14" t="n">
-        <v>1.119787923964032</v>
+        <v>1.21933567662261</v>
       </c>
       <c r="F14" t="n">
-        <v>1.495894311365146</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.5997357992073977</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.526978247718487</v>
+        <v>1.677155551215701</v>
       </c>
       <c r="E15" t="n">
-        <v>1.078305589720859</v>
+        <v>0.9889410482332623</v>
       </c>
       <c r="F15" t="n">
-        <v>10.69120877534373</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.539762219286658</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.515231013709259</v>
+        <v>1.677155551215701</v>
       </c>
       <c r="E16" t="n">
-        <v>1.088481806158546</v>
+        <v>0.9889410482332623</v>
       </c>
       <c r="F16" t="n">
-        <v>11.02208789780936</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.557160448000002</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>2.788882870469681</v>
+        <v>2.877062786837223</v>
       </c>
       <c r="E17" t="n">
-        <v>1.549559135150269</v>
+        <v>1.590527480795106</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.091163648000006</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="18">
@@ -892,16 +892,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="E20" t="n">
-        <v>1.10227038425243</v>
+        <v>1.224744871391589</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="21">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7.999999940395354</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>2.791666651936292</v>
+        <v>2.875</v>
       </c>
       <c r="E21" t="n">
-        <v>2.113120378114275</v>
+        <v>2.179449471770337</v>
       </c>
       <c r="F21" t="n">
-        <v>4.666666712053297</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12.0004880537106</v>
+        <v>12</v>
       </c>
       <c r="D22" t="n">
-        <v>2.541758128936128</v>
+        <v>2.625</v>
       </c>
       <c r="E22" t="n">
-        <v>2.265480510229244</v>
+        <v>2.29128784747792</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.333821578249033</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="23">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.846153846153846</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>1.695512820512821</v>
+        <v>1.75</v>
       </c>
       <c r="E23" t="n">
-        <v>1.666999473675202</v>
+        <v>1.75</v>
       </c>
       <c r="F23" t="n">
-        <v>10.82051282051282</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -988,16 +988,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.661538461538461</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>1.763461538461538</v>
+        <v>1.75</v>
       </c>
       <c r="E24" t="n">
-        <v>1.701578626595082</v>
+        <v>1.75</v>
       </c>
       <c r="F24" t="n">
-        <v>11.13846153846154</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.525</v>
+        <v>1.5625</v>
       </c>
       <c r="E25" t="n">
-        <v>1.16940155635265</v>
+        <v>1.192424001771182</v>
       </c>
       <c r="F25" t="n">
-        <v>5.199999999999999</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
